--- a/www/flightdata/xlsx/eoss-378.xlsx
+++ b/www/flightdata/xlsx/eoss-378.xlsx
@@ -2100,7 +2100,7 @@
         <v>27177.49</v>
       </c>
       <c r="I2">
-        <v>331</v>
+        <v>214</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>

--- a/www/flightdata/xlsx/eoss-378.xlsx
+++ b/www/flightdata/xlsx/eoss-378.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="537">
   <si>
     <t>flight</t>
   </si>
@@ -57,6 +57,21 @@
     <t>range_distance_traveled_km</t>
   </si>
   <si>
+    <t>parachute.description</t>
+  </si>
+  <si>
+    <t>parachute.size_ft</t>
+  </si>
+  <si>
+    <t>parachute.size_m</t>
+  </si>
+  <si>
+    <t>parachute.weight_lb</t>
+  </si>
+  <si>
+    <t>parachute.weight_kg</t>
+  </si>
+  <si>
     <t>weights.client_lb</t>
   </si>
   <si>
@@ -99,6 +114,15 @@
     <t>weights.necklift_kg</t>
   </si>
   <si>
+    <t>detected_burst.detected</t>
+  </si>
+  <si>
+    <t>detected_burst.burst_ft</t>
+  </si>
+  <si>
+    <t>detected_burst.burst_m</t>
+  </si>
+  <si>
     <t>launch_location.latitude</t>
   </si>
   <si>
@@ -148,6 +172,12 @@
   </si>
   <si>
     <t>2hrs 27mins 30secs</t>
+  </si>
+  <si>
+    <t>Rocketman</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>flightid</t>
@@ -1958,10 +1988,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2073,25 +2103,49 @@
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:45">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>89165</v>
@@ -2103,7 +2157,7 @@
         <v>214</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K2">
         <v>8850</v>
@@ -2114,76 +2168,100 @@
       <c r="M2">
         <v>30.7</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2">
+        <v>3.66</v>
+      </c>
+      <c r="Q2">
+        <v>1.81</v>
+      </c>
+      <c r="R2">
+        <v>0.82</v>
+      </c>
+      <c r="S2">
         <v>1.31</v>
       </c>
-      <c r="O2">
+      <c r="T2">
         <v>0.59</v>
       </c>
-      <c r="P2">
+      <c r="U2">
         <v>2.35</v>
       </c>
-      <c r="Q2">
+      <c r="V2">
         <v>1.07</v>
       </c>
-      <c r="R2">
+      <c r="W2">
         <v>1.81</v>
       </c>
-      <c r="S2">
+      <c r="X2">
         <v>0.82</v>
       </c>
-      <c r="T2">
+      <c r="Y2">
         <v>5.46</v>
       </c>
-      <c r="U2">
+      <c r="Z2">
         <v>2.48</v>
       </c>
-      <c r="V2">
+      <c r="AA2">
         <v>4.41</v>
       </c>
-      <c r="W2">
+      <c r="AB2">
         <v>2</v>
       </c>
-      <c r="X2">
+      <c r="AC2">
         <v>9.869999999999999</v>
       </c>
-      <c r="Y2">
+      <c r="AD2">
         <v>4.48</v>
       </c>
-      <c r="Z2">
+      <c r="AE2">
         <v>7.93</v>
       </c>
-      <c r="AA2">
+      <c r="AF2">
         <v>3.6</v>
       </c>
-      <c r="AB2">
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
         <v>38.14616667</v>
       </c>
-      <c r="AC2">
+      <c r="AK2">
         <v>-97.77293333</v>
       </c>
-      <c r="AD2">
+      <c r="AL2">
         <v>2927</v>
       </c>
-      <c r="AE2">
+      <c r="AM2">
         <v>892.15</v>
       </c>
-      <c r="AF2">
+      <c r="AN2">
         <v>38.19725</v>
       </c>
-      <c r="AG2">
+      <c r="AO2">
         <v>-97.42755</v>
       </c>
-      <c r="AH2">
+      <c r="AP2">
         <v>19.08</v>
       </c>
-      <c r="AI2">
+      <c r="AQ2">
         <v>30.7</v>
       </c>
-      <c r="AJ2">
+      <c r="AR2">
         <v>2948</v>
       </c>
-      <c r="AK2">
+      <c r="AS2">
         <v>898.55</v>
       </c>
     </row>
@@ -2199,156 +2277,156 @@
   <sheetData>
     <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2">
         <v>45822.49983796296</v>
@@ -2369,16 +2447,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="L2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="M2">
         <v>75</v>
@@ -2414,7 +2492,7 @@
         <v>5.62866667</v>
       </c>
       <c r="AE2" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AG2">
         <v>18.466667</v>
@@ -2431,10 +2509,10 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C3" s="2">
         <v>45822.50018518518</v>
@@ -2455,16 +2533,16 @@
         <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="M3">
         <v>71</v>
@@ -2500,7 +2578,7 @@
         <v>5.395</v>
       </c>
       <c r="AE3" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF3">
         <v>-0.025556</v>
@@ -2541,10 +2619,10 @@
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2">
         <v>45822.50053240741</v>
@@ -2565,16 +2643,16 @@
         <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="L4" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="M4">
         <v>55</v>
@@ -2610,7 +2688,7 @@
         <v>5.527</v>
       </c>
       <c r="AE4" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF4">
         <v>0.014444</v>
@@ -2663,10 +2741,10 @@
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2">
         <v>45822.50087962963</v>
@@ -2687,16 +2765,16 @@
         <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="M5">
         <v>73</v>
@@ -2732,7 +2810,7 @@
         <v>5.80133333</v>
       </c>
       <c r="AE5" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF5">
         <v>0.03</v>
@@ -2785,10 +2863,10 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2">
         <v>45822.50122685185</v>
@@ -2809,16 +2887,16 @@
         <v>120</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="M6">
         <v>63</v>
@@ -2854,7 +2932,7 @@
         <v>6.50233333</v>
       </c>
       <c r="AE6" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF6">
         <v>0.076667</v>
@@ -2907,10 +2985,10 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2">
         <v>45822.50157407407</v>
@@ -2931,16 +3009,16 @@
         <v>150</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L7" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="M7">
         <v>75</v>
@@ -2976,7 +3054,7 @@
         <v>5.87266667</v>
       </c>
       <c r="AE7" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF7">
         <v>-0.06888900000000001</v>
@@ -3029,10 +3107,10 @@
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2">
         <v>45822.50192129629</v>
@@ -3053,16 +3131,16 @@
         <v>180</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L8" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="M8">
         <v>113</v>
@@ -3098,7 +3176,7 @@
         <v>5.852</v>
       </c>
       <c r="AE8" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF8">
         <v>-0.002222</v>
@@ -3151,10 +3229,10 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>45822.50226851852</v>
@@ -3175,16 +3253,16 @@
         <v>210</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="L9" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="M9">
         <v>74</v>
@@ -3220,7 +3298,7 @@
         <v>6.29933333</v>
       </c>
       <c r="AE9" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF9">
         <v>0.048889</v>
@@ -3273,10 +3351,10 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2">
         <v>45822.50261574074</v>
@@ -3297,16 +3375,16 @@
         <v>240</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L10" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="M10">
         <v>102</v>
@@ -3342,7 +3420,7 @@
         <v>5.63866667</v>
       </c>
       <c r="AE10" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF10">
         <v>-0.07222199999999999</v>
@@ -3395,10 +3473,10 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2">
         <v>45822.50331018519</v>
@@ -3419,16 +3497,16 @@
         <v>300</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L11" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="M11">
         <v>77</v>
@@ -3464,7 +3542,7 @@
         <v>6.538</v>
       </c>
       <c r="AE11" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF11">
         <v>0.049167</v>
@@ -3517,10 +3595,10 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2">
         <v>45822.5036574074</v>
@@ -3541,16 +3619,16 @@
         <v>330</v>
       </c>
       <c r="I12" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="M12">
         <v>101</v>
@@ -3586,7 +3664,7 @@
         <v>6.83766667</v>
       </c>
       <c r="AE12" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF12">
         <v>0.032778</v>
@@ -3639,10 +3717,10 @@
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C13" s="2">
         <v>45822.50400462963</v>
@@ -3663,16 +3741,16 @@
         <v>360</v>
       </c>
       <c r="I13" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="L13" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="M13">
         <v>116</v>
@@ -3708,7 +3786,7 @@
         <v>6.63433333</v>
       </c>
       <c r="AE13" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF13">
         <v>-0.022222</v>
@@ -3761,10 +3839,10 @@
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2">
         <v>45822.50469907407</v>
@@ -3785,16 +3863,16 @@
         <v>420</v>
       </c>
       <c r="I14" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="L14" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="M14">
         <v>127</v>
@@ -3830,7 +3908,7 @@
         <v>6.16716667</v>
       </c>
       <c r="AE14" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF14">
         <v>-0.025556</v>
@@ -3883,10 +3961,10 @@
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C15" s="2">
         <v>45822.5050462963</v>
@@ -3907,16 +3985,16 @@
         <v>450</v>
       </c>
       <c r="I15" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="L15" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="M15">
         <v>117</v>
@@ -3952,7 +4030,7 @@
         <v>6.38066667</v>
       </c>
       <c r="AE15" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF15">
         <v>0.023333</v>
@@ -4005,10 +4083,10 @@
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C16" s="2">
         <v>45822.50539351852</v>
@@ -4029,16 +4107,16 @@
         <v>480</v>
       </c>
       <c r="I16" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L16" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="M16">
         <v>113</v>
@@ -4074,7 +4152,7 @@
         <v>6.096</v>
       </c>
       <c r="AE16" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF16">
         <v>-0.031111</v>
@@ -4127,10 +4205,10 @@
     </row>
     <row r="17" spans="1:47">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C17" s="2">
         <v>45822.50574074074</v>
@@ -4151,16 +4229,16 @@
         <v>510</v>
       </c>
       <c r="I17" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="L17" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="M17">
         <v>122</v>
@@ -4196,7 +4274,7 @@
         <v>6.44133333</v>
       </c>
       <c r="AE17" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF17">
         <v>0.037778</v>
@@ -4249,10 +4327,10 @@
     </row>
     <row r="18" spans="1:47">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C18" s="2">
         <v>45822.50643518518</v>
@@ -4273,16 +4351,16 @@
         <v>570</v>
       </c>
       <c r="I18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L18" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="M18">
         <v>109</v>
@@ -4318,7 +4396,7 @@
         <v>6.62933333</v>
       </c>
       <c r="AE18" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF18">
         <v>0.010278</v>
@@ -4371,10 +4449,10 @@
     </row>
     <row r="19" spans="1:47">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C19" s="2">
         <v>45822.50678240741</v>
@@ -4395,16 +4473,16 @@
         <v>600</v>
       </c>
       <c r="I19" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L19" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="M19">
         <v>110</v>
@@ -4440,7 +4518,7 @@
         <v>6.70566667</v>
       </c>
       <c r="AE19" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF19">
         <v>0.008333</v>
@@ -4493,10 +4571,10 @@
     </row>
     <row r="20" spans="1:47">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C20" s="2">
         <v>45822.50712962963</v>
@@ -4517,16 +4595,16 @@
         <v>630</v>
       </c>
       <c r="I20" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="L20" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="M20">
         <v>131</v>
@@ -4562,7 +4640,7 @@
         <v>6.56333333</v>
       </c>
       <c r="AE20" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF20">
         <v>-0.015556</v>
@@ -4615,10 +4693,10 @@
     </row>
     <row r="21" spans="1:47">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C21" s="2">
         <v>45822.50747685185</v>
@@ -4639,16 +4717,16 @@
         <v>660</v>
       </c>
       <c r="I21" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="L21" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="M21">
         <v>118</v>
@@ -4684,7 +4762,7 @@
         <v>6.49233333</v>
       </c>
       <c r="AE21" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF21">
         <v>-0.007778</v>
@@ -4737,10 +4815,10 @@
     </row>
     <row r="22" spans="1:47">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2">
         <v>45822.50782407408</v>
@@ -4761,16 +4839,16 @@
         <v>690</v>
       </c>
       <c r="I22" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="L22" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="M22">
         <v>137</v>
@@ -4806,7 +4884,7 @@
         <v>6.30933333</v>
       </c>
       <c r="AE22" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF22">
         <v>-0.02</v>
@@ -4859,10 +4937,10 @@
     </row>
     <row r="23" spans="1:47">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2">
         <v>45822.50817129629</v>
@@ -4883,16 +4961,16 @@
         <v>720</v>
       </c>
       <c r="I23" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="L23" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="M23">
         <v>128</v>
@@ -4928,7 +5006,7 @@
         <v>5.86233333</v>
       </c>
       <c r="AE23" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF23">
         <v>-0.048889</v>
@@ -4981,10 +5059,10 @@
     </row>
     <row r="24" spans="1:47">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2">
         <v>45822.50851851852</v>
@@ -5005,16 +5083,16 @@
         <v>750</v>
       </c>
       <c r="I24" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="L24" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="M24">
         <v>101</v>
@@ -5050,7 +5128,7 @@
         <v>6.218</v>
       </c>
       <c r="AE24" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF24">
         <v>0.038889</v>
@@ -5103,10 +5181,10 @@
     </row>
     <row r="25" spans="1:47">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C25" s="2">
         <v>45822.50886574074</v>
@@ -5127,16 +5205,16 @@
         <v>780</v>
       </c>
       <c r="I25" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="L25" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="M25">
         <v>86</v>
@@ -5172,7 +5250,7 @@
         <v>6.492</v>
       </c>
       <c r="AE25" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF25">
         <v>0.03</v>
@@ -5225,10 +5303,10 @@
     </row>
     <row r="26" spans="1:47">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C26" s="2">
         <v>45822.50921296296</v>
@@ -5249,16 +5327,16 @@
         <v>810</v>
       </c>
       <c r="I26" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L26" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="M26">
         <v>85</v>
@@ -5294,7 +5372,7 @@
         <v>6.55333333</v>
       </c>
       <c r="AE26" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF26">
         <v>0.006667</v>
@@ -5347,10 +5425,10 @@
     </row>
     <row r="27" spans="1:47">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C27" s="2">
         <v>45822.50956018519</v>
@@ -5371,16 +5449,16 @@
         <v>840</v>
       </c>
       <c r="I27" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="L27" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="M27">
         <v>90</v>
@@ -5416,7 +5494,7 @@
         <v>6.87833333</v>
       </c>
       <c r="AE27" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF27">
         <v>0.035556</v>
@@ -5469,10 +5547,10 @@
     </row>
     <row r="28" spans="1:47">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C28" s="2">
         <v>45822.50990740741</v>
@@ -5493,16 +5571,16 @@
         <v>870</v>
       </c>
       <c r="I28" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L28" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="M28">
         <v>77</v>
@@ -5538,7 +5616,7 @@
         <v>7.15266667</v>
       </c>
       <c r="AE28" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF28">
         <v>0.03</v>
@@ -5591,10 +5669,10 @@
     </row>
     <row r="29" spans="1:47">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C29" s="2">
         <v>45822.51060185185</v>
@@ -5615,16 +5693,16 @@
         <v>930</v>
       </c>
       <c r="I29" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="L29" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="M29">
         <v>119</v>
@@ -5660,7 +5738,7 @@
         <v>7.12716667</v>
       </c>
       <c r="AE29" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF29">
         <v>-0.001389</v>
@@ -5713,10 +5791,10 @@
     </row>
     <row r="30" spans="1:47">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C30" s="2">
         <v>45822.51094907407</v>
@@ -5737,16 +5815,16 @@
         <v>960</v>
       </c>
       <c r="I30" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="L30" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="M30">
         <v>130</v>
@@ -5782,7 +5860,7 @@
         <v>7.09166667</v>
       </c>
       <c r="AE30" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF30">
         <v>-0.003889</v>
@@ -5835,10 +5913,10 @@
     </row>
     <row r="31" spans="1:47">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C31" s="2">
         <v>45822.5112962963</v>
@@ -5859,16 +5937,16 @@
         <v>990</v>
       </c>
       <c r="I31" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="L31" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="M31">
         <v>104</v>
@@ -5904,7 +5982,7 @@
         <v>7.09166667</v>
       </c>
       <c r="AE31" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF31">
         <v>0</v>
@@ -5957,10 +6035,10 @@
     </row>
     <row r="32" spans="1:47">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C32" s="2">
         <v>45822.51164351852</v>
@@ -5981,16 +6059,16 @@
         <v>1020</v>
       </c>
       <c r="I32" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="L32" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="M32">
         <v>94</v>
@@ -6026,7 +6104,7 @@
         <v>6.49233333</v>
       </c>
       <c r="AE32" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF32">
         <v>-0.065556</v>
@@ -6079,10 +6157,10 @@
     </row>
     <row r="33" spans="1:47">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C33" s="2">
         <v>45822.51268518518</v>
@@ -6103,16 +6181,16 @@
         <v>1110</v>
       </c>
       <c r="I33" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="M33">
         <v>83</v>
@@ -6148,7 +6226,7 @@
         <v>6.82077778</v>
       </c>
       <c r="AE33" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF33">
         <v>0.011975</v>
@@ -6201,10 +6279,10 @@
     </row>
     <row r="34" spans="1:47">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C34" s="2">
         <v>45822.5144212963</v>
@@ -6225,16 +6303,16 @@
         <v>1260</v>
       </c>
       <c r="I34" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="L34" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="M34">
         <v>77</v>
@@ -6270,7 +6348,7 @@
         <v>7.35786667</v>
       </c>
       <c r="AE34" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF34">
         <v>0.011748</v>
@@ -6323,10 +6401,10 @@
     </row>
     <row r="35" spans="1:47">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C35" s="2">
         <v>45822.51476851852</v>
@@ -6347,16 +6425,16 @@
         <v>1290</v>
       </c>
       <c r="I35" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="L35" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="M35">
         <v>78</v>
@@ -6392,7 +6470,7 @@
         <v>7.41666667</v>
       </c>
       <c r="AE35" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF35">
         <v>0.006444</v>
@@ -6445,10 +6523,10 @@
     </row>
     <row r="36" spans="1:47">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C36" s="2">
         <v>45822.51546296296</v>
@@ -6469,16 +6547,16 @@
         <v>1350</v>
       </c>
       <c r="I36" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L36" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="M36">
         <v>36</v>
@@ -6514,7 +6592,7 @@
         <v>7.9705</v>
       </c>
       <c r="AE36" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF36">
         <v>0.030278</v>
@@ -6567,10 +6645,10 @@
     </row>
     <row r="37" spans="1:47">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C37" s="2">
         <v>45822.51581018518</v>
@@ -6591,16 +6669,16 @@
         <v>1380</v>
       </c>
       <c r="I37" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="L37" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="M37">
         <v>78</v>
@@ -6636,7 +6714,7 @@
         <v>8.13833333</v>
       </c>
       <c r="AE37" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF37">
         <v>0.018333</v>
@@ -6689,10 +6767,10 @@
     </row>
     <row r="38" spans="1:47">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C38" s="2">
         <v>45822.51615740741</v>
@@ -6713,16 +6791,16 @@
         <v>1410</v>
       </c>
       <c r="I38" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="L38" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="M38">
         <v>66</v>
@@ -6758,7 +6836,7 @@
         <v>7.63</v>
       </c>
       <c r="AE38" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF38">
         <v>-0.055556</v>
@@ -6811,10 +6889,10 @@
     </row>
     <row r="39" spans="1:47">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C39" s="2">
         <v>45822.51650462963</v>
@@ -6835,16 +6913,16 @@
         <v>1440</v>
       </c>
       <c r="I39" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="L39" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="M39">
         <v>45</v>
@@ -6880,7 +6958,7 @@
         <v>7.417</v>
       </c>
       <c r="AE39" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF39">
         <v>-0.023333</v>
@@ -6933,10 +7011,10 @@
     </row>
     <row r="40" spans="1:47">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C40" s="2">
         <v>45822.51685185185</v>
@@ -6957,16 +7035,16 @@
         <v>1470</v>
       </c>
       <c r="I40" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="L40" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="M40">
         <v>35</v>
@@ -7002,7 +7080,7 @@
         <v>7.28466667</v>
       </c>
       <c r="AE40" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF40">
         <v>-0.014444</v>
@@ -7055,10 +7133,10 @@
     </row>
     <row r="41" spans="1:47">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C41" s="2">
         <v>45822.51719907407</v>
@@ -7079,16 +7157,16 @@
         <v>1500</v>
       </c>
       <c r="I41" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="L41" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="M41">
         <v>11</v>
@@ -7124,7 +7202,7 @@
         <v>7.38633333</v>
       </c>
       <c r="AE41" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF41">
         <v>0.011111</v>
@@ -7177,10 +7255,10 @@
     </row>
     <row r="42" spans="1:47">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C42" s="2">
         <v>45822.51754629629</v>
@@ -7201,16 +7279,16 @@
         <v>1530</v>
       </c>
       <c r="I42" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="L42" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="M42">
         <v>335</v>
@@ -7246,7 +7324,7 @@
         <v>7.50833333</v>
       </c>
       <c r="AE42" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF42">
         <v>0.013333</v>
@@ -7299,10 +7377,10 @@
     </row>
     <row r="43" spans="1:47">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C43" s="2">
         <v>45822.51789351852</v>
@@ -7323,16 +7401,16 @@
         <v>1560</v>
       </c>
       <c r="I43" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="L43" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="M43">
         <v>315</v>
@@ -7368,7 +7446,7 @@
         <v>7.54866667</v>
       </c>
       <c r="AE43" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF43">
         <v>0.004444</v>
@@ -7421,10 +7499,10 @@
     </row>
     <row r="44" spans="1:47">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C44" s="2">
         <v>45822.51824074074</v>
@@ -7445,16 +7523,16 @@
         <v>1590</v>
       </c>
       <c r="I44" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="L44" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="M44">
         <v>330</v>
@@ -7490,7 +7568,7 @@
         <v>7.295</v>
       </c>
       <c r="AE44" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF44">
         <v>-0.027778</v>
@@ -7543,10 +7621,10 @@
     </row>
     <row r="45" spans="1:47">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C45" s="2">
         <v>45822.51858796296</v>
@@ -7567,16 +7645,16 @@
         <v>1620</v>
       </c>
       <c r="I45" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L45" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M45">
         <v>359</v>
@@ -7612,7 +7690,7 @@
         <v>7.41666667</v>
       </c>
       <c r="AE45" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF45">
         <v>0.013333</v>
@@ -7665,10 +7743,10 @@
     </row>
     <row r="46" spans="1:47">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C46" s="2">
         <v>45822.51893518519</v>
@@ -7689,16 +7767,16 @@
         <v>1650</v>
       </c>
       <c r="I46" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="L46" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="M46">
         <v>326</v>
@@ -7734,7 +7812,7 @@
         <v>7.85366667</v>
       </c>
       <c r="AE46" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF46">
         <v>0.047778</v>
@@ -7787,10 +7865,10 @@
     </row>
     <row r="47" spans="1:47">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C47" s="2">
         <v>45822.51962962963</v>
@@ -7811,16 +7889,16 @@
         <v>1710</v>
       </c>
       <c r="I47" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="L47" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="M47">
         <v>334</v>
@@ -7856,7 +7934,7 @@
         <v>8.01633333</v>
       </c>
       <c r="AE47" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF47">
         <v>0.008888999999999999</v>
@@ -7909,10 +7987,10 @@
     </row>
     <row r="48" spans="1:47">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C48" s="2">
         <v>45822.51997685185</v>
@@ -7933,16 +8011,16 @@
         <v>1740</v>
       </c>
       <c r="I48" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="L48" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="M48">
         <v>354</v>
@@ -7978,7 +8056,7 @@
         <v>7.72166667</v>
       </c>
       <c r="AE48" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF48">
         <v>-0.032222</v>
@@ -8031,10 +8109,10 @@
     </row>
     <row r="49" spans="1:48">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C49" s="2">
         <v>45822.5206712963</v>
@@ -8055,16 +8133,16 @@
         <v>1800</v>
       </c>
       <c r="I49" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="L49" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="M49">
         <v>51</v>
@@ -8100,7 +8178,7 @@
         <v>8.7325</v>
       </c>
       <c r="AE49" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF49">
         <v>0.055278</v>
@@ -8153,10 +8231,10 @@
     </row>
     <row r="50" spans="1:48">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C50" s="2">
         <v>45822.52101851852</v>
@@ -8177,16 +8255,16 @@
         <v>1830</v>
       </c>
       <c r="I50" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="L50" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="M50">
         <v>94</v>
@@ -8222,7 +8300,7 @@
         <v>9.428333329999999</v>
       </c>
       <c r="AE50" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF50">
         <v>0.076111</v>
@@ -8275,10 +8353,10 @@
     </row>
     <row r="51" spans="1:48">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C51" s="2">
         <v>45822.52206018518</v>
@@ -8299,16 +8377,16 @@
         <v>1920</v>
       </c>
       <c r="I51" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="L51" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M51">
         <v>103</v>
@@ -8344,7 +8422,7 @@
         <v>9.001777779999999</v>
       </c>
       <c r="AE51" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AF51">
         <v>-0.015556</v>
@@ -8397,10 +8475,10 @@
     </row>
     <row r="52" spans="1:48">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C52" s="2">
         <v>45822.52275462963</v>
@@ -8421,16 +8499,16 @@
         <v>1980</v>
       </c>
       <c r="I52" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="L52" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="M52">
         <v>66</v>
@@ -8466,7 +8544,7 @@
         <v>6.61416667</v>
       </c>
       <c r="AE52" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF52">
         <v>-0.130556</v>
@@ -8517,15 +8595,15 @@
         <v>6.622995</v>
       </c>
       <c r="AV52" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="53" spans="1:48">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C53" s="2">
         <v>45822.52344907408</v>
@@ -8546,16 +8624,16 @@
         <v>2040</v>
       </c>
       <c r="I53" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="L53" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="M53">
         <v>97</v>
@@ -8591,7 +8669,7 @@
         <v>4.94283333</v>
       </c>
       <c r="AE53" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF53">
         <v>-0.091389</v>
@@ -8644,10 +8722,10 @@
     </row>
     <row r="54" spans="1:48">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C54" s="2">
         <v>45822.52414351852</v>
@@ -8668,16 +8746,16 @@
         <v>2100</v>
       </c>
       <c r="I54" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="L54" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="M54">
         <v>84</v>
@@ -8713,7 +8791,7 @@
         <v>4.01316667</v>
       </c>
       <c r="AE54" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF54">
         <v>-0.050833</v>
@@ -8766,10 +8844,10 @@
     </row>
     <row r="55" spans="1:48">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C55" s="2">
         <v>45822.52587962963</v>
@@ -8790,16 +8868,16 @@
         <v>2250</v>
       </c>
       <c r="I55" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="L55" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="M55">
         <v>162</v>
@@ -8835,7 +8913,7 @@
         <v>5.71193333</v>
       </c>
       <c r="AE55" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF55">
         <v>0.037156</v>
@@ -8888,10 +8966,10 @@
     </row>
     <row r="56" spans="1:48">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C56" s="2">
         <v>45822.52622685185</v>
@@ -8912,16 +8990,16 @@
         <v>2280</v>
       </c>
       <c r="I56" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="L56" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="M56">
         <v>116</v>
@@ -8957,7 +9035,7 @@
         <v>4.938</v>
       </c>
       <c r="AE56" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF56">
         <v>-0.08466700000000001</v>
@@ -9010,10 +9088,10 @@
     </row>
     <row r="57" spans="1:48">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C57" s="2">
         <v>45822.52657407407</v>
@@ -9034,16 +9112,16 @@
         <v>2310</v>
       </c>
       <c r="I57" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="L57" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="M57">
         <v>112</v>
@@ -9079,7 +9157,7 @@
         <v>4.826</v>
       </c>
       <c r="AE57" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF57">
         <v>-0.012222</v>
@@ -9132,10 +9210,10 @@
     </row>
     <row r="58" spans="1:48">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C58" s="2">
         <v>45822.5269212963</v>
@@ -9156,16 +9234,16 @@
         <v>2340</v>
       </c>
       <c r="I58" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L58" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M58">
         <v>156</v>
@@ -9201,7 +9279,7 @@
         <v>6.53266667</v>
       </c>
       <c r="AE58" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF58">
         <v>0.186667</v>
@@ -9254,10 +9332,10 @@
     </row>
     <row r="59" spans="1:48">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C59" s="2">
         <v>45822.52761574074</v>
@@ -9278,16 +9356,16 @@
         <v>2400</v>
       </c>
       <c r="I59" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="L59" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="M59">
         <v>194</v>
@@ -9323,7 +9401,7 @@
         <v>5.2985</v>
       </c>
       <c r="AE59" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF59">
         <v>-0.0675</v>
@@ -9376,10 +9454,10 @@
     </row>
     <row r="60" spans="1:48">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C60" s="2">
         <v>45822.52796296297</v>
@@ -9400,16 +9478,16 @@
         <v>2430</v>
       </c>
       <c r="I60" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="L60" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="M60">
         <v>218</v>
@@ -9445,7 +9523,7 @@
         <v>5.212</v>
       </c>
       <c r="AE60" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF60">
         <v>-0.009443999999999999</v>
@@ -9498,10 +9576,10 @@
     </row>
     <row r="61" spans="1:48">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C61" s="2">
         <v>45822.52831018518</v>
@@ -9522,16 +9600,16 @@
         <v>2460</v>
       </c>
       <c r="I61" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="L61" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M61">
         <v>307</v>
@@ -9567,7 +9645,7 @@
         <v>5.842</v>
       </c>
       <c r="AE61" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF61">
         <v>0.06888900000000001</v>
@@ -9620,10 +9698,10 @@
     </row>
     <row r="62" spans="1:48">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C62" s="2">
         <v>45822.52900462963</v>
@@ -9644,16 +9722,16 @@
         <v>2520</v>
       </c>
       <c r="I62" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="L62" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="M62">
         <v>150</v>
@@ -9689,7 +9767,7 @@
         <v>6.55833333</v>
       </c>
       <c r="AE62" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF62">
         <v>0.039167</v>
@@ -9742,10 +9820,10 @@
     </row>
     <row r="63" spans="1:48">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C63" s="2">
         <v>45822.52935185185</v>
@@ -9766,16 +9844,16 @@
         <v>2550</v>
       </c>
       <c r="I63" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="L63" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="M63">
         <v>203</v>
@@ -9811,7 +9889,7 @@
         <v>5.22233333</v>
       </c>
       <c r="AE63" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF63">
         <v>-0.146111</v>
@@ -9864,10 +9942,10 @@
     </row>
     <row r="64" spans="1:48">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C64" s="2">
         <v>45822.5300462963</v>
@@ -9888,16 +9966,16 @@
         <v>2610</v>
       </c>
       <c r="I64" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="L64" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M64">
         <v>196</v>
@@ -9933,7 +10011,7 @@
         <v>4.892</v>
       </c>
       <c r="AE64" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF64">
         <v>-0.018056</v>
@@ -9986,10 +10064,10 @@
     </row>
     <row r="65" spans="1:47">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C65" s="2">
         <v>45822.53143518518</v>
@@ -10010,16 +10088,16 @@
         <v>2730</v>
       </c>
       <c r="I65" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="L65" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="M65">
         <v>61</v>
@@ -10055,7 +10133,7 @@
         <v>4.86916667</v>
       </c>
       <c r="AE65" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF65">
         <v>-0.000625</v>
@@ -10108,10 +10186,10 @@
     </row>
     <row r="66" spans="1:47">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C66" s="2">
         <v>45822.53178240741</v>
@@ -10132,16 +10210,16 @@
         <v>2760</v>
       </c>
       <c r="I66" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="L66" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="M66">
         <v>97</v>
@@ -10177,7 +10255,7 @@
         <v>5.29333333</v>
       </c>
       <c r="AE66" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF66">
         <v>0.046389</v>
@@ -10230,10 +10308,10 @@
     </row>
     <row r="67" spans="1:47">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C67" s="2">
         <v>45822.53212962963</v>
@@ -10254,16 +10332,16 @@
         <v>2790</v>
       </c>
       <c r="I67" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="L67" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="M67">
         <v>285</v>
@@ -10299,7 +10377,7 @@
         <v>5.53733333</v>
       </c>
       <c r="AE67" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF67">
         <v>0.026667</v>
@@ -10352,10 +10430,10 @@
     </row>
     <row r="68" spans="1:47">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C68" s="2">
         <v>45822.53282407407</v>
@@ -10376,16 +10454,16 @@
         <v>2850</v>
       </c>
       <c r="I68" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L68" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M68">
         <v>355</v>
@@ -10421,7 +10499,7 @@
         <v>5.47616667</v>
       </c>
       <c r="AE68" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF68">
         <v>-0.003333</v>
@@ -10474,10 +10552,10 @@
     </row>
     <row r="69" spans="1:47">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C69" s="2">
         <v>45822.53317129629</v>
@@ -10498,16 +10576,16 @@
         <v>2880</v>
       </c>
       <c r="I69" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="L69" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="M69">
         <v>305</v>
@@ -10543,7 +10621,7 @@
         <v>5.08</v>
       </c>
       <c r="AE69" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF69">
         <v>-0.043333</v>
@@ -10596,10 +10674,10 @@
     </row>
     <row r="70" spans="1:47">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C70" s="2">
         <v>45822.53456018519</v>
@@ -10620,16 +10698,16 @@
         <v>3000</v>
       </c>
       <c r="I70" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="L70" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="M70">
         <v>16</v>
@@ -10665,7 +10743,7 @@
         <v>4.39675</v>
       </c>
       <c r="AE70" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF70">
         <v>-0.018681</v>
@@ -10718,10 +10796,10 @@
     </row>
     <row r="71" spans="1:47">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C71" s="2">
         <v>45822.53525462963</v>
@@ -10742,16 +10820,16 @@
         <v>3060</v>
       </c>
       <c r="I71" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="L71" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="M71">
         <v>181</v>
@@ -10787,7 +10865,7 @@
         <v>4.85133333</v>
       </c>
       <c r="AE71" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF71">
         <v>0.024861</v>
@@ -10840,10 +10918,10 @@
     </row>
     <row r="72" spans="1:47">
       <c r="A72" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C72" s="2">
         <v>45822.5362962963</v>
@@ -10864,16 +10942,16 @@
         <v>3150</v>
       </c>
       <c r="I72" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L72" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M72">
         <v>244</v>
@@ -10909,7 +10987,7 @@
         <v>3.70844444</v>
       </c>
       <c r="AE72" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF72">
         <v>-0.041667</v>
@@ -10962,10 +11040,10 @@
     </row>
     <row r="73" spans="1:47">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C73" s="2">
         <v>45822.53664351852</v>
@@ -10986,16 +11064,16 @@
         <v>3180</v>
       </c>
       <c r="I73" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="L73" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="M73">
         <v>190</v>
@@ -11031,7 +11109,7 @@
         <v>4.22666667</v>
       </c>
       <c r="AE73" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF73">
         <v>0.056667</v>
@@ -11084,10 +11162,10 @@
     </row>
     <row r="74" spans="1:47">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C74" s="2">
         <v>45822.53699074074</v>
@@ -11108,16 +11186,16 @@
         <v>3210</v>
       </c>
       <c r="I74" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="L74" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="M74">
         <v>293</v>
@@ -11153,7 +11231,7 @@
         <v>4.81566667</v>
       </c>
       <c r="AE74" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF74">
         <v>0.064444</v>
@@ -11206,10 +11284,10 @@
     </row>
     <row r="75" spans="1:47">
       <c r="A75" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C75" s="2">
         <v>45822.53768518518</v>
@@ -11230,16 +11308,16 @@
         <v>3270</v>
       </c>
       <c r="I75" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="L75" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="M75">
         <v>342</v>
@@ -11275,7 +11353,7 @@
         <v>5.588</v>
       </c>
       <c r="AE75" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF75">
         <v>0.042222</v>
@@ -11328,10 +11406,10 @@
     </row>
     <row r="76" spans="1:47">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C76" s="2">
         <v>45822.53803240741</v>
@@ -11352,16 +11430,16 @@
         <v>3300</v>
       </c>
       <c r="I76" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="L76" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="M76">
         <v>326</v>
@@ -11397,7 +11475,7 @@
         <v>5.34433333</v>
       </c>
       <c r="AE76" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF76">
         <v>-0.026667</v>
@@ -11450,10 +11528,10 @@
     </row>
     <row r="77" spans="1:47">
       <c r="A77" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C77" s="2">
         <v>45822.53837962963</v>
@@ -11474,16 +11552,16 @@
         <v>3330</v>
       </c>
       <c r="I77" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="L77" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="M77">
         <v>313</v>
@@ -11519,7 +11597,7 @@
         <v>5.00866667</v>
       </c>
       <c r="AE77" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF77">
         <v>-0.036667</v>
@@ -11572,10 +11650,10 @@
     </row>
     <row r="78" spans="1:47">
       <c r="A78" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C78" s="2">
         <v>45822.53872685185</v>
@@ -11596,16 +11674,16 @@
         <v>3360</v>
       </c>
       <c r="I78" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L78" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="M78">
         <v>346</v>
@@ -11641,7 +11719,7 @@
         <v>4.83633333</v>
       </c>
       <c r="AE78" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF78">
         <v>-0.018889</v>
@@ -11694,10 +11772,10 @@
     </row>
     <row r="79" spans="1:47">
       <c r="A79" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C79" s="2">
         <v>45822.53907407408</v>
@@ -11718,16 +11796,16 @@
         <v>3390</v>
       </c>
       <c r="I79" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="L79" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="M79">
         <v>314</v>
@@ -11763,7 +11841,7 @@
         <v>4.47033333</v>
       </c>
       <c r="AE79" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF79">
         <v>-0.04</v>
@@ -11816,10 +11894,10 @@
     </row>
     <row r="80" spans="1:47">
       <c r="A80" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C80" s="2">
         <v>45822.54046296296</v>
@@ -11840,16 +11918,16 @@
         <v>3510</v>
       </c>
       <c r="I80" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="L80" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="M80">
         <v>287</v>
@@ -11885,7 +11963,7 @@
         <v>4.732</v>
       </c>
       <c r="AE80" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF80">
         <v>0.007153</v>
@@ -11938,10 +12016,10 @@
     </row>
     <row r="81" spans="1:47">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B81" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C81" s="2">
         <v>45822.54081018519</v>
@@ -11962,16 +12040,16 @@
         <v>3540</v>
       </c>
       <c r="I81" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="L81" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="M81">
         <v>291</v>
@@ -12007,7 +12085,7 @@
         <v>6.25866667</v>
       </c>
       <c r="AE81" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF81">
         <v>0.166944</v>
@@ -12060,10 +12138,10 @@
     </row>
     <row r="82" spans="1:47">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C82" s="2">
         <v>45822.54150462963</v>
@@ -12084,16 +12162,16 @@
         <v>3600</v>
       </c>
       <c r="I82" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="L82" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="M82">
         <v>293</v>
@@ -12129,7 +12207,7 @@
         <v>5.85216667</v>
       </c>
       <c r="AE82" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF82">
         <v>-0.022222</v>
@@ -12182,10 +12260,10 @@
     </row>
     <row r="83" spans="1:47">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C83" s="2">
         <v>45822.54185185185</v>
@@ -12206,16 +12284,16 @@
         <v>3630</v>
       </c>
       <c r="I83" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="L83" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="M83">
         <v>284</v>
@@ -12251,7 +12329,7 @@
         <v>5.55766667</v>
       </c>
       <c r="AE83" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF83">
         <v>-0.032222</v>
@@ -12304,10 +12382,10 @@
     </row>
     <row r="84" spans="1:47">
       <c r="A84" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C84" s="2">
         <v>45822.5425462963</v>
@@ -12328,16 +12406,16 @@
         <v>3690</v>
       </c>
       <c r="I84" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L84" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="M84">
         <v>320</v>
@@ -12373,7 +12451,7 @@
         <v>4.93766667</v>
       </c>
       <c r="AE84" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF84">
         <v>-0.033889</v>
@@ -12426,10 +12504,10 @@
     </row>
     <row r="85" spans="1:47">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C85" s="2">
         <v>45822.54289351852</v>
@@ -12450,16 +12528,16 @@
         <v>3720</v>
       </c>
       <c r="I85" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="L85" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="M85">
         <v>261</v>
@@ -12495,7 +12573,7 @@
         <v>4.58233333</v>
       </c>
       <c r="AE85" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF85">
         <v>-0.038889</v>
@@ -12548,10 +12626,10 @@
     </row>
     <row r="86" spans="1:47">
       <c r="A86" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C86" s="2">
         <v>45822.54497685185</v>
@@ -12572,16 +12650,16 @@
         <v>3900</v>
       </c>
       <c r="I86" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="L86" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="M86">
         <v>239</v>
@@ -12617,7 +12695,7 @@
         <v>4.58383333</v>
       </c>
       <c r="AE86" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF86">
         <v>3.1E-05</v>
@@ -12670,10 +12748,10 @@
     </row>
     <row r="87" spans="1:47">
       <c r="A87" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C87" s="2">
         <v>45822.54532407408</v>
@@ -12694,16 +12772,16 @@
         <v>3930</v>
       </c>
       <c r="I87" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L87" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="M87">
         <v>276</v>
@@ -12739,7 +12817,7 @@
         <v>5.79133333</v>
       </c>
       <c r="AE87" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF87">
         <v>0.132037</v>
@@ -12792,10 +12870,10 @@
     </row>
     <row r="88" spans="1:47">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B88" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C88" s="2">
         <v>45822.5456712963</v>
@@ -12816,16 +12894,16 @@
         <v>3960</v>
       </c>
       <c r="I88" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="L88" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="M88">
         <v>283</v>
@@ -12861,7 +12939,7 @@
         <v>5.96366667</v>
       </c>
       <c r="AE88" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF88">
         <v>0.018889</v>
@@ -12914,10 +12992,10 @@
     </row>
     <row r="89" spans="1:47">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C89" s="2">
         <v>45822.54601851852</v>
@@ -12938,16 +13016,16 @@
         <v>3990</v>
       </c>
       <c r="I89" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="L89" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="M89">
         <v>272</v>
@@ -12983,7 +13061,7 @@
         <v>5.903</v>
       </c>
       <c r="AE89" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF89">
         <v>-0.006667</v>
@@ -13036,10 +13114,10 @@
     </row>
     <row r="90" spans="1:47">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C90" s="2">
         <v>45822.54636574074</v>
@@ -13060,16 +13138,16 @@
         <v>4020</v>
       </c>
       <c r="I90" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="L90" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="M90">
         <v>272</v>
@@ -13105,7 +13183,7 @@
         <v>5.61866667</v>
       </c>
       <c r="AE90" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF90">
         <v>-0.031111</v>
@@ -13158,10 +13236,10 @@
     </row>
     <row r="91" spans="1:47">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C91" s="2">
         <v>45822.54671296296</v>
@@ -13182,16 +13260,16 @@
         <v>4050</v>
       </c>
       <c r="I91" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J91" t="b">
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="L91" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="M91">
         <v>291</v>
@@ -13227,7 +13305,7 @@
         <v>5.43533333</v>
       </c>
       <c r="AE91" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF91">
         <v>-0.02</v>
@@ -13280,10 +13358,10 @@
     </row>
     <row r="92" spans="1:47">
       <c r="A92" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C92" s="2">
         <v>45822.54706018518</v>
@@ -13304,16 +13382,16 @@
         <v>4080</v>
       </c>
       <c r="I92" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J92" t="b">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="L92" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="M92">
         <v>276</v>
@@ -13349,7 +13427,7 @@
         <v>5.141</v>
       </c>
       <c r="AE92" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF92">
         <v>-0.032222</v>
@@ -13402,10 +13480,10 @@
     </row>
     <row r="93" spans="1:47">
       <c r="A93" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C93" s="2">
         <v>45822.54775462963</v>
@@ -13426,16 +13504,16 @@
         <v>4140</v>
       </c>
       <c r="I93" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J93" t="b">
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="L93" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="M93">
         <v>246</v>
@@ -13471,7 +13549,7 @@
         <v>4.60766667</v>
       </c>
       <c r="AE93" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF93">
         <v>-0.029167</v>
@@ -13524,10 +13602,10 @@
     </row>
     <row r="94" spans="1:47">
       <c r="A94" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C94" s="2">
         <v>45822.54810185185</v>
@@ -13548,16 +13626,16 @@
         <v>4170</v>
       </c>
       <c r="I94" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J94" t="b">
         <v>1</v>
       </c>
       <c r="K94" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L94" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="M94">
         <v>304</v>
@@ -13593,7 +13671,7 @@
         <v>4.826</v>
       </c>
       <c r="AE94" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF94">
         <v>0.023889</v>
@@ -13646,10 +13724,10 @@
     </row>
     <row r="95" spans="1:47">
       <c r="A95" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B95" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C95" s="2">
         <v>45822.54844907407</v>
@@ -13670,16 +13748,16 @@
         <v>4200</v>
       </c>
       <c r="I95" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J95" t="b">
         <v>1</v>
       </c>
       <c r="K95" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="L95" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="M95">
         <v>301</v>
@@ -13715,7 +13793,7 @@
         <v>5.151</v>
       </c>
       <c r="AE95" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF95">
         <v>0.035556</v>
@@ -13768,10 +13846,10 @@
     </row>
     <row r="96" spans="1:47">
       <c r="A96" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B96" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C96" s="2">
         <v>45822.54879629629</v>
@@ -13792,16 +13870,16 @@
         <v>4230</v>
       </c>
       <c r="I96" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J96" t="b">
         <v>1</v>
       </c>
       <c r="K96" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="L96" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="M96">
         <v>286</v>
@@ -13837,7 +13915,7 @@
         <v>5.24266667</v>
       </c>
       <c r="AE96" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF96">
         <v>0.01</v>
@@ -13890,10 +13968,10 @@
     </row>
     <row r="97" spans="1:47">
       <c r="A97" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C97" s="2">
         <v>45822.54949074074</v>
@@ -13914,16 +13992,16 @@
         <v>4290</v>
       </c>
       <c r="I97" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J97" t="b">
         <v>1</v>
       </c>
       <c r="K97" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L97" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="M97">
         <v>294</v>
@@ -13959,7 +14037,7 @@
         <v>5.60316667</v>
       </c>
       <c r="AE97" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF97">
         <v>0.019722</v>
@@ -14012,10 +14090,10 @@
     </row>
     <row r="98" spans="1:47">
       <c r="A98" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B98" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C98" s="2">
         <v>45822.54983796296</v>
@@ -14036,16 +14114,16 @@
         <v>4320</v>
       </c>
       <c r="I98" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J98" t="b">
         <v>1</v>
       </c>
       <c r="K98" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="L98" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="M98">
         <v>241</v>
@@ -14081,7 +14159,7 @@
         <v>5.35433333</v>
       </c>
       <c r="AE98" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF98">
         <v>-0.027222</v>
@@ -14134,10 +14212,10 @@
     </row>
     <row r="99" spans="1:47">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B99" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C99" s="2">
         <v>45822.55018518519</v>
@@ -14158,16 +14236,16 @@
         <v>4350</v>
       </c>
       <c r="I99" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J99" t="b">
         <v>1</v>
       </c>
       <c r="K99" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="L99" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="M99">
         <v>253</v>
@@ -14203,7 +14281,7 @@
         <v>5.466</v>
       </c>
       <c r="AE99" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF99">
         <v>0.012222</v>
@@ -14256,10 +14334,10 @@
     </row>
     <row r="100" spans="1:47">
       <c r="A100" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B100" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C100" s="2">
         <v>45822.5505324074</v>
@@ -14280,16 +14358,16 @@
         <v>4380</v>
       </c>
       <c r="I100" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J100" t="b">
         <v>1</v>
       </c>
       <c r="K100" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="L100" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="M100">
         <v>251</v>
@@ -14325,7 +14403,7 @@
         <v>5.08</v>
       </c>
       <c r="AE100" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF100">
         <v>-0.042222</v>
@@ -14378,10 +14456,10 @@
     </row>
     <row r="101" spans="1:47">
       <c r="A101" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B101" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C101" s="2">
         <v>45822.55087962963</v>
@@ -14402,16 +14480,16 @@
         <v>4410</v>
       </c>
       <c r="I101" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J101" t="b">
         <v>1</v>
       </c>
       <c r="K101" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="L101" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="M101">
         <v>257</v>
@@ -14447,7 +14525,7 @@
         <v>4.125</v>
       </c>
       <c r="AE101" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AF101">
         <v>-0.104444</v>
@@ -14510,156 +14588,156 @@
   <sheetData>
     <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2">
         <v>45822.55122685185</v>
@@ -14680,16 +14758,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="L2" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="M2">
         <v>283</v>
@@ -14725,7 +14803,7 @@
         <v>-10.63733333</v>
       </c>
       <c r="AE2" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AG2">
         <v>-34.9</v>
@@ -14742,10 +14820,10 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C3" s="2">
         <v>45822.55157407407</v>
@@ -14766,16 +14844,16 @@
         <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="L3" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="M3">
         <v>193</v>
@@ -14811,7 +14889,7 @@
         <v>-22.667</v>
       </c>
       <c r="AE3" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF3">
         <v>-1.315556</v>
@@ -14852,10 +14930,10 @@
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2">
         <v>45822.5519212963</v>
@@ -14876,16 +14954,16 @@
         <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="L4" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="M4">
         <v>294</v>
@@ -14921,7 +14999,7 @@
         <v>-21.12266667</v>
       </c>
       <c r="AE4" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF4">
         <v>0.168889</v>
@@ -14974,10 +15052,10 @@
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2">
         <v>45822.55226851852</v>
@@ -14998,16 +15076,16 @@
         <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="L5" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="M5">
         <v>332</v>
@@ -15043,7 +15121,7 @@
         <v>-14.854</v>
       </c>
       <c r="AE5" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF5">
         <v>0.6855560000000001</v>
@@ -15096,10 +15174,10 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2">
         <v>45822.55331018518</v>
@@ -15120,16 +15198,16 @@
         <v>180</v>
       </c>
       <c r="I6" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="L6" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="M6">
         <v>314</v>
@@ -15165,7 +15243,7 @@
         <v>-18.59277778</v>
       </c>
       <c r="AE6" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF6">
         <v>-0.136296</v>
@@ -15218,10 +15296,10 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2">
         <v>45822.55400462963</v>
@@ -15242,16 +15320,16 @@
         <v>240</v>
       </c>
       <c r="I7" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="L7" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="M7">
         <v>310</v>
@@ -15287,7 +15365,7 @@
         <v>-15.56516667</v>
       </c>
       <c r="AE7" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF7">
         <v>0.165556</v>
@@ -15340,10 +15418,10 @@
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2">
         <v>45822.55435185185</v>
@@ -15364,16 +15442,16 @@
         <v>270</v>
       </c>
       <c r="I8" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="L8" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="M8">
         <v>323</v>
@@ -15409,7 +15487,7 @@
         <v>-12.964</v>
       </c>
       <c r="AE8" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF8">
         <v>0.284444</v>
@@ -15462,10 +15540,10 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>45822.55469907408</v>
@@ -15486,16 +15564,16 @@
         <v>300</v>
       </c>
       <c r="I9" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="L9" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="M9">
         <v>334</v>
@@ -15531,7 +15609,7 @@
         <v>-14.20366667</v>
       </c>
       <c r="AE9" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF9">
         <v>-0.135556</v>
@@ -15584,10 +15662,10 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2">
         <v>45822.55504629629</v>
@@ -15608,16 +15686,16 @@
         <v>330</v>
       </c>
       <c r="I10" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="L10" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="M10">
         <v>349</v>
@@ -15653,7 +15731,7 @@
         <v>-13.17766667</v>
       </c>
       <c r="AE10" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF10">
         <v>0.112222</v>
@@ -15706,10 +15784,10 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2">
         <v>45822.55539351852</v>
@@ -15730,16 +15808,16 @@
         <v>360</v>
       </c>
       <c r="I11" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="L11" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="M11">
         <v>77</v>
@@ -15775,7 +15853,7 @@
         <v>-11.867</v>
       </c>
       <c r="AE11" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF11">
         <v>0.143333</v>
@@ -15828,10 +15906,10 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2">
         <v>45822.55574074074</v>
@@ -15852,16 +15930,16 @@
         <v>390</v>
       </c>
       <c r="I12" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="L12" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="M12">
         <v>122</v>
@@ -15897,7 +15975,7 @@
         <v>-12.37466667</v>
       </c>
       <c r="AE12" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF12">
         <v>-0.055556</v>
@@ -15950,10 +16028,10 @@
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C13" s="2">
         <v>45822.55608796296</v>
@@ -15974,16 +16052,16 @@
         <v>420</v>
       </c>
       <c r="I13" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="L13" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="M13">
         <v>309</v>
@@ -16019,7 +16097,7 @@
         <v>-13.78733333</v>
       </c>
       <c r="AE13" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF13">
         <v>-0.154444</v>
@@ -16072,10 +16150,10 @@
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2">
         <v>45822.55678240741</v>
@@ -16096,16 +16174,16 @@
         <v>480</v>
       </c>
       <c r="I14" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="L14" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="M14">
         <v>212</v>
@@ -16141,7 +16219,7 @@
         <v>-12.3545</v>
       </c>
       <c r="AE14" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF14">
         <v>0.078333</v>
@@ -16194,10 +16272,10 @@
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C15" s="2">
         <v>45822.55712962963</v>
@@ -16218,16 +16296,16 @@
         <v>510</v>
       </c>
       <c r="I15" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="L15" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="M15">
         <v>200</v>
@@ -16263,7 +16341,7 @@
         <v>-11.176</v>
       </c>
       <c r="AE15" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF15">
         <v>0.128889</v>
@@ -16316,10 +16394,10 @@
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C16" s="2">
         <v>45822.5581712963</v>
@@ -16340,16 +16418,16 @@
         <v>600</v>
       </c>
       <c r="I16" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="L16" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="M16">
         <v>181</v>
@@ -16385,7 +16463,7 @@
         <v>-9.445444439999999</v>
       </c>
       <c r="AE16" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF16">
         <v>0.063086</v>
@@ -16438,10 +16516,10 @@
     </row>
     <row r="17" spans="1:47">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C17" s="2">
         <v>45822.55851851852</v>
@@ -16462,16 +16540,16 @@
         <v>630</v>
       </c>
       <c r="I17" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="L17" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="M17">
         <v>156</v>
@@ -16507,7 +16585,7 @@
         <v>-8.717000000000001</v>
       </c>
       <c r="AE17" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF17">
         <v>0.07963000000000001</v>
@@ -16560,10 +16638,10 @@
     </row>
     <row r="18" spans="1:47">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C18" s="2">
         <v>45822.55886574074</v>
@@ -16584,16 +16662,16 @@
         <v>660</v>
       </c>
       <c r="I18" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="L18" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="M18">
         <v>131</v>
@@ -16629,7 +16707,7 @@
         <v>-8.311</v>
       </c>
       <c r="AE18" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF18">
         <v>0.044444</v>
@@ -16682,10 +16760,10 @@
     </row>
     <row r="19" spans="1:47">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C19" s="2">
         <v>45822.55956018518</v>
@@ -16706,16 +16784,16 @@
         <v>720</v>
       </c>
       <c r="I19" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="L19" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="M19">
         <v>280</v>
@@ -16751,7 +16829,7 @@
         <v>-8.07216667</v>
       </c>
       <c r="AE19" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF19">
         <v>0.013056</v>
@@ -16804,10 +16882,10 @@
     </row>
     <row r="20" spans="1:47">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C20" s="2">
         <v>45822.55990740741</v>
@@ -16828,16 +16906,16 @@
         <v>750</v>
       </c>
       <c r="I20" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="L20" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="M20">
         <v>205</v>
@@ -16873,7 +16951,7 @@
         <v>-7.77233333</v>
       </c>
       <c r="AE20" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF20">
         <v>0.032778</v>
@@ -16926,10 +17004,10 @@
     </row>
     <row r="21" spans="1:47">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C21" s="2">
         <v>45822.56025462963</v>
@@ -16950,16 +17028,16 @@
         <v>780</v>
       </c>
       <c r="I21" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="L21" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="M21">
         <v>179</v>
@@ -16995,7 +17073,7 @@
         <v>-7.70133333</v>
       </c>
       <c r="AE21" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF21">
         <v>0.007778</v>
@@ -17048,10 +17126,10 @@
     </row>
     <row r="22" spans="1:47">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2">
         <v>45822.56094907408</v>
@@ -17072,16 +17150,16 @@
         <v>840</v>
       </c>
       <c r="I22" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="L22" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="M22">
         <v>74</v>
@@ -17117,7 +17195,7 @@
         <v>-7.44216667</v>
       </c>
       <c r="AE22" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF22">
         <v>0.014167</v>
@@ -17170,10 +17248,10 @@
     </row>
     <row r="23" spans="1:47">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2">
         <v>45822.5612962963</v>
@@ -17194,16 +17272,16 @@
         <v>870</v>
       </c>
       <c r="I23" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="L23" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="M23">
         <v>89</v>
@@ -17239,7 +17317,7 @@
         <v>-7.72166667</v>
       </c>
       <c r="AE23" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF23">
         <v>-0.030556</v>
@@ -17292,10 +17370,10 @@
     </row>
     <row r="24" spans="1:47">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2">
         <v>45822.56164351852</v>
@@ -17316,16 +17394,16 @@
         <v>900</v>
       </c>
       <c r="I24" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="L24" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="M24">
         <v>232</v>
@@ -17361,7 +17439,7 @@
         <v>-7.76233333</v>
       </c>
       <c r="AE24" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF24">
         <v>-0.004444</v>
@@ -17414,10 +17492,10 @@
     </row>
     <row r="25" spans="1:47">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C25" s="2">
         <v>45822.56268518518</v>
@@ -17438,16 +17516,16 @@
         <v>990</v>
       </c>
       <c r="I25" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="L25" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="M25">
         <v>125</v>
@@ -17483,7 +17561,7 @@
         <v>-7.52511111</v>
       </c>
       <c r="AE25" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF25">
         <v>0.008642</v>
@@ -17536,10 +17614,10 @@
     </row>
     <row r="26" spans="1:47">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C26" s="2">
         <v>45822.56303240741</v>
@@ -17560,16 +17638,16 @@
         <v>1020</v>
       </c>
       <c r="I26" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="L26" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="M26">
         <v>104</v>
@@ -17605,7 +17683,7 @@
         <v>-7.20333333</v>
       </c>
       <c r="AE26" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF26">
         <v>0.035185</v>
@@ -17658,10 +17736,10 @@
     </row>
     <row r="27" spans="1:47">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C27" s="2">
         <v>45822.56337962963</v>
@@ -17682,16 +17760,16 @@
         <v>1050</v>
       </c>
       <c r="I27" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="L27" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="M27">
         <v>70</v>
@@ -17727,7 +17805,7 @@
         <v>-7.163</v>
       </c>
       <c r="AE27" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF27">
         <v>0.004444</v>
@@ -17780,10 +17858,10 @@
     </row>
     <row r="28" spans="1:47">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C28" s="2">
         <v>45822.56476851852</v>
@@ -17804,16 +17882,16 @@
         <v>1170</v>
       </c>
       <c r="I28" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="L28" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="M28">
         <v>88</v>
@@ -17849,7 +17927,7 @@
         <v>-6.51</v>
       </c>
       <c r="AE28" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF28">
         <v>0.017847</v>
@@ -17902,10 +17980,10 @@
     </row>
     <row r="29" spans="1:47">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C29" s="2">
         <v>45822.56511574074</v>
@@ -17926,16 +18004,16 @@
         <v>1200</v>
       </c>
       <c r="I29" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="L29" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="M29">
         <v>77</v>
@@ -17971,7 +18049,7 @@
         <v>-6.75633333</v>
       </c>
       <c r="AE29" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF29">
         <v>-0.026944</v>
@@ -18024,10 +18102,10 @@
     </row>
     <row r="30" spans="1:47">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C30" s="2">
         <v>45822.56546296296</v>
@@ -18048,16 +18126,16 @@
         <v>1230</v>
       </c>
       <c r="I30" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="L30" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="M30">
         <v>73</v>
@@ -18093,7 +18171,7 @@
         <v>-5.98433333</v>
       </c>
       <c r="AE30" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF30">
         <v>0.08444400000000001</v>
@@ -18146,10 +18224,10 @@
     </row>
     <row r="31" spans="1:47">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C31" s="2">
         <v>45822.5661574074</v>
@@ -18170,16 +18248,16 @@
         <v>1290</v>
       </c>
       <c r="I31" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="L31" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="M31">
         <v>3</v>
@@ -18215,7 +18293,7 @@
         <v>-5.91816667</v>
       </c>
       <c r="AE31" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF31">
         <v>0.003611</v>
@@ -18268,10 +18346,10 @@
     </row>
     <row r="32" spans="1:47">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C32" s="2">
         <v>45822.56685185185</v>
@@ -18292,16 +18370,16 @@
         <v>1350</v>
       </c>
       <c r="I32" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="L32" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="M32">
         <v>353</v>
@@ -18337,7 +18415,7 @@
         <v>-5.3595</v>
       </c>
       <c r="AE32" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF32">
         <v>0.030556</v>
@@ -18390,10 +18468,10 @@
     </row>
     <row r="33" spans="1:47">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C33" s="2">
         <v>45822.56719907407</v>
@@ -18414,16 +18492,16 @@
         <v>1380</v>
       </c>
       <c r="I33" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="L33" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="M33">
         <v>318</v>
@@ -18459,7 +18537,7 @@
         <v>-5.69966667</v>
       </c>
       <c r="AE33" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF33">
         <v>-0.037222</v>
@@ -18512,10 +18590,10 @@
     </row>
     <row r="34" spans="1:47">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C34" s="2">
         <v>45822.56789351852</v>
@@ -18536,16 +18614,16 @@
         <v>1440</v>
       </c>
       <c r="I34" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="L34" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="M34">
         <v>352</v>
@@ -18581,7 +18659,7 @@
         <v>-5.81666667</v>
       </c>
       <c r="AE34" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF34">
         <v>-0.006389</v>
@@ -18634,10 +18712,10 @@
     </row>
     <row r="35" spans="1:47">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C35" s="2">
         <v>45822.56858796296</v>
@@ -18658,16 +18736,16 @@
         <v>1500</v>
       </c>
       <c r="I35" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="L35" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="M35">
         <v>331</v>
@@ -18703,7 +18781,7 @@
         <v>-5.79616667</v>
       </c>
       <c r="AE35" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF35">
         <v>0.001111</v>
@@ -18756,10 +18834,10 @@
     </row>
     <row r="36" spans="1:47">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C36" s="2">
         <v>45822.56893518518</v>
@@ -18780,16 +18858,16 @@
         <v>1530</v>
       </c>
       <c r="I36" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="L36" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="M36">
         <v>352</v>
@@ -18825,7 +18903,7 @@
         <v>-5.68966667</v>
       </c>
       <c r="AE36" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF36">
         <v>0.011667</v>
@@ -18878,10 +18956,10 @@
     </row>
     <row r="37" spans="1:47">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C37" s="2">
         <v>45822.56928240741</v>
@@ -18902,16 +18980,16 @@
         <v>1560</v>
       </c>
       <c r="I37" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="L37" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="M37">
         <v>336</v>
@@ -18947,7 +19025,7 @@
         <v>-6.18733333</v>
       </c>
       <c r="AE37" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF37">
         <v>-0.054444</v>
@@ -19000,10 +19078,10 @@
     </row>
     <row r="38" spans="1:47">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C38" s="2">
         <v>45822.56962962963</v>
@@ -19024,16 +19102,16 @@
         <v>1590</v>
       </c>
       <c r="I38" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="L38" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="M38">
         <v>340</v>
@@ -19069,7 +19147,7 @@
         <v>-6.218</v>
       </c>
       <c r="AE38" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF38">
         <v>-0.003333</v>
@@ -19122,10 +19200,10 @@
     </row>
     <row r="39" spans="1:47">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C39" s="2">
         <v>45822.56997685185</v>
@@ -19146,16 +19224,16 @@
         <v>1620</v>
       </c>
       <c r="I39" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="L39" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="M39">
         <v>342</v>
@@ -19191,7 +19269,7 @@
         <v>-5.44566667</v>
       </c>
       <c r="AE39" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF39">
         <v>0.08444400000000001</v>
@@ -19244,10 +19322,10 @@
     </row>
     <row r="40" spans="1:47">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C40" s="2">
         <v>45822.57032407408</v>
@@ -19268,16 +19346,16 @@
         <v>1650</v>
       </c>
       <c r="I40" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="L40" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="M40">
         <v>15</v>
@@ -19313,7 +19391,7 @@
         <v>-4.938</v>
       </c>
       <c r="AE40" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF40">
         <v>0.055556</v>
@@ -19366,10 +19444,10 @@
     </row>
     <row r="41" spans="1:47">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C41" s="2">
         <v>45822.57101851852</v>
@@ -19390,16 +19468,16 @@
         <v>1710</v>
       </c>
       <c r="I41" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="L41" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="M41">
         <v>353</v>
@@ -19435,7 +19513,7 @@
         <v>-4.99866667</v>
       </c>
       <c r="AE41" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF41">
         <v>-0.003333</v>
@@ -19488,10 +19566,10 @@
     </row>
     <row r="42" spans="1:47">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C42" s="2">
         <v>45822.57136574074</v>
@@ -19512,16 +19590,16 @@
         <v>1740</v>
       </c>
       <c r="I42" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="L42" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="M42">
         <v>8</v>
@@ -19557,7 +19635,7 @@
         <v>-5.29333333</v>
       </c>
       <c r="AE42" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF42">
         <v>-0.032222</v>
@@ -19610,10 +19688,10 @@
     </row>
     <row r="43" spans="1:47">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C43" s="2">
         <v>45822.57310185185</v>
@@ -19634,16 +19712,16 @@
         <v>1890</v>
       </c>
       <c r="I43" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="L43" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="M43">
         <v>51</v>
@@ -19679,7 +19757,7 @@
         <v>-4.99873333</v>
       </c>
       <c r="AE43" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF43">
         <v>0.006444</v>
@@ -19732,10 +19810,10 @@
     </row>
     <row r="44" spans="1:47">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C44" s="2">
         <v>45822.5737962963</v>
@@ -19756,16 +19834,16 @@
         <v>1950</v>
       </c>
       <c r="I44" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="L44" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="M44">
         <v>39</v>
@@ -19801,7 +19879,7 @@
         <v>-4.2875</v>
       </c>
       <c r="AE44" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF44">
         <v>0.038889</v>
@@ -19854,10 +19932,10 @@
     </row>
     <row r="45" spans="1:47">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C45" s="2">
         <v>45822.57414351852</v>
@@ -19878,16 +19956,16 @@
         <v>1980</v>
       </c>
       <c r="I45" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="L45" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="M45">
         <v>66</v>
@@ -19923,7 +20001,7 @@
         <v>-3.627</v>
       </c>
       <c r="AE45" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF45">
         <v>0.07222199999999999</v>
@@ -19976,10 +20054,10 @@
     </row>
     <row r="46" spans="1:47">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C46" s="2">
         <v>45822.57449074074</v>
@@ -20000,16 +20078,16 @@
         <v>2010</v>
       </c>
       <c r="I46" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="L46" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="M46">
         <v>52</v>
@@ -20045,7 +20123,7 @@
         <v>-4.60266667</v>
       </c>
       <c r="AE46" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF46">
         <v>-0.106667</v>
@@ -20098,10 +20176,10 @@
     </row>
     <row r="47" spans="1:47">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C47" s="2">
         <v>45822.57483796297</v>
@@ -20122,16 +20200,16 @@
         <v>2040</v>
       </c>
       <c r="I47" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="L47" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="M47">
         <v>55</v>
@@ -20167,7 +20245,7 @@
         <v>-4.54133333</v>
       </c>
       <c r="AE47" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF47">
         <v>0.006667</v>
@@ -20220,10 +20298,10 @@
     </row>
     <row r="48" spans="1:47">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C48" s="2">
         <v>45822.57518518518</v>
@@ -20244,16 +20322,16 @@
         <v>2070</v>
       </c>
       <c r="I48" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="L48" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="M48">
         <v>67</v>
@@ -20289,7 +20367,7 @@
         <v>-4.04366667</v>
       </c>
       <c r="AE48" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF48">
         <v>0.054444</v>
@@ -20342,10 +20420,10 @@
     </row>
     <row r="49" spans="1:47">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C49" s="2">
         <v>45822.57553240741</v>
@@ -20366,16 +20444,16 @@
         <v>2100</v>
       </c>
       <c r="I49" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="L49" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="M49">
         <v>51</v>
@@ -20411,7 +20489,7 @@
         <v>-4.89733333</v>
       </c>
       <c r="AE49" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF49">
         <v>-0.093333</v>
@@ -20464,10 +20542,10 @@
     </row>
     <row r="50" spans="1:47">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C50" s="2">
         <v>45822.57622685185</v>
@@ -20488,16 +20566,16 @@
         <v>2160</v>
       </c>
       <c r="I50" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="L50" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="M50">
         <v>67</v>
@@ -20533,7 +20611,7 @@
         <v>-4.56183333</v>
       </c>
       <c r="AE50" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF50">
         <v>0.018333</v>
@@ -20586,10 +20664,10 @@
     </row>
     <row r="51" spans="1:47">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C51" s="2">
         <v>45822.57657407408</v>
@@ -20610,16 +20688,16 @@
         <v>2190</v>
       </c>
       <c r="I51" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="L51" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="M51">
         <v>93</v>
@@ -20655,7 +20733,7 @@
         <v>-4.29766667</v>
       </c>
       <c r="AE51" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF51">
         <v>0.028889</v>
@@ -20708,10 +20786,10 @@
     </row>
     <row r="52" spans="1:47">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C52" s="2">
         <v>45822.5769212963</v>
@@ -20732,16 +20810,16 @@
         <v>2220</v>
       </c>
       <c r="I52" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="L52" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="M52">
         <v>81</v>
@@ -20777,7 +20855,7 @@
         <v>-4.572</v>
       </c>
       <c r="AE52" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF52">
         <v>-0.03</v>
@@ -20830,10 +20908,10 @@
     </row>
     <row r="53" spans="1:47">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C53" s="2">
         <v>45822.57726851852</v>
@@ -20854,16 +20932,16 @@
         <v>2250</v>
       </c>
       <c r="I53" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="L53" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="M53">
         <v>105</v>
@@ -20899,7 +20977,7 @@
         <v>-4.35866667</v>
       </c>
       <c r="AE53" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF53">
         <v>0.023333</v>
@@ -20952,10 +21030,10 @@
     </row>
     <row r="54" spans="1:47">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C54" s="2">
         <v>45822.57761574074</v>
@@ -20976,16 +21054,16 @@
         <v>2280</v>
       </c>
       <c r="I54" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="L54" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="M54">
         <v>101</v>
@@ -21021,7 +21099,7 @@
         <v>-4.389</v>
       </c>
       <c r="AE54" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF54">
         <v>-0.003333</v>
@@ -21074,10 +21152,10 @@
     </row>
     <row r="55" spans="1:47">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C55" s="2">
         <v>45822.57796296296</v>
@@ -21098,16 +21176,16 @@
         <v>2310</v>
       </c>
       <c r="I55" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="L55" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="M55">
         <v>101</v>
@@ -21143,7 +21221,7 @@
         <v>-4.14533333</v>
       </c>
       <c r="AE55" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF55">
         <v>0.026667</v>
@@ -21196,10 +21274,10 @@
     </row>
     <row r="56" spans="1:47">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C56" s="2">
         <v>45822.57831018518</v>
@@ -21220,16 +21298,16 @@
         <v>2340</v>
       </c>
       <c r="I56" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="L56" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="M56">
         <v>125</v>
@@ -21265,7 +21343,7 @@
         <v>-4.10466667</v>
       </c>
       <c r="AE56" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF56">
         <v>0.004444</v>
@@ -21318,10 +21396,10 @@
     </row>
     <row r="57" spans="1:47">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C57" s="2">
         <v>45822.57900462963</v>
@@ -21342,16 +21420,16 @@
         <v>2400</v>
       </c>
       <c r="I57" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="L57" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="M57">
         <v>125</v>
@@ -21387,7 +21465,7 @@
         <v>-3.88116667</v>
       </c>
       <c r="AE57" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF57">
         <v>0.012222</v>
@@ -21440,10 +21518,10 @@
     </row>
     <row r="58" spans="1:47">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C58" s="2">
         <v>45822.57969907407</v>
@@ -21464,16 +21542,16 @@
         <v>2460</v>
       </c>
       <c r="I58" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="L58" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="M58">
         <v>127</v>
@@ -21509,7 +21587,7 @@
         <v>-3.79466667</v>
       </c>
       <c r="AE58" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF58">
         <v>0.004722</v>
@@ -21562,10 +21640,10 @@
     </row>
     <row r="59" spans="1:47">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C59" s="2">
         <v>45822.58004629629</v>
@@ -21586,16 +21664,16 @@
         <v>2490</v>
       </c>
       <c r="I59" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="L59" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="M59">
         <v>120</v>
@@ -21631,7 +21709,7 @@
         <v>-4.14533333</v>
       </c>
       <c r="AE59" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF59">
         <v>-0.038333</v>
@@ -21684,10 +21762,10 @@
     </row>
     <row r="60" spans="1:47">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C60" s="2">
         <v>45822.58039351852</v>
@@ -21708,16 +21786,16 @@
         <v>2520</v>
       </c>
       <c r="I60" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="L60" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="M60">
         <v>116</v>
@@ -21753,7 +21831,7 @@
         <v>-4.125</v>
       </c>
       <c r="AE60" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF60">
         <v>0.002222</v>
@@ -21806,10 +21884,10 @@
     </row>
     <row r="61" spans="1:47">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C61" s="2">
         <v>45822.58074074074</v>
@@ -21830,16 +21908,16 @@
         <v>2550</v>
       </c>
       <c r="I61" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="L61" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="M61">
         <v>112</v>
@@ -21875,7 +21953,7 @@
         <v>-4.064</v>
       </c>
       <c r="AE61" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF61">
         <v>0.006667</v>
@@ -21928,10 +22006,10 @@
     </row>
     <row r="62" spans="1:47">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C62" s="2">
         <v>45822.58108796296</v>
@@ -21952,16 +22030,16 @@
         <v>2580</v>
       </c>
       <c r="I62" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="L62" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="M62">
         <v>112</v>
@@ -21997,7 +22075,7 @@
         <v>-3.99266667</v>
       </c>
       <c r="AE62" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF62">
         <v>0.007778</v>
@@ -22050,10 +22128,10 @@
     </row>
     <row r="63" spans="1:47">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C63" s="2">
         <v>45822.58143518519</v>
@@ -22074,16 +22152,16 @@
         <v>2610</v>
       </c>
       <c r="I63" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="L63" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="M63">
         <v>103</v>
@@ -22119,7 +22197,7 @@
         <v>-4.08433333</v>
       </c>
       <c r="AE63" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF63">
         <v>-0.01</v>
@@ -22172,10 +22250,10 @@
     </row>
     <row r="64" spans="1:47">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C64" s="2">
         <v>45822.5817824074</v>
@@ -22196,16 +22274,16 @@
         <v>2640</v>
       </c>
       <c r="I64" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="L64" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="M64">
         <v>116</v>
@@ -22241,7 +22319,7 @@
         <v>-3.88133333</v>
       </c>
       <c r="AE64" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF64">
         <v>0.022222</v>
@@ -22294,10 +22372,10 @@
     </row>
     <row r="65" spans="1:47">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C65" s="2">
         <v>45822.58212962963</v>
@@ -22318,16 +22396,16 @@
         <v>2670</v>
       </c>
       <c r="I65" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="L65" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="M65">
         <v>113</v>
@@ -22363,7 +22441,7 @@
         <v>-3.78966667</v>
       </c>
       <c r="AE65" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF65">
         <v>0.01</v>
@@ -22416,10 +22494,10 @@
     </row>
     <row r="66" spans="1:47">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C66" s="2">
         <v>45822.58247685185</v>
@@ -22440,16 +22518,16 @@
         <v>2700</v>
       </c>
       <c r="I66" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="L66" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="M66">
         <v>96</v>
@@ -22485,7 +22563,7 @@
         <v>-3.84033333</v>
       </c>
       <c r="AE66" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF66">
         <v>-0.005556</v>
@@ -22538,10 +22616,10 @@
     </row>
     <row r="67" spans="1:47">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C67" s="2">
         <v>45822.58282407407</v>
@@ -22562,16 +22640,16 @@
         <v>2730</v>
       </c>
       <c r="I67" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="L67" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="M67">
         <v>128</v>
@@ -22607,7 +22685,7 @@
         <v>-3.69833333</v>
       </c>
       <c r="AE67" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF67">
         <v>0.015556</v>
@@ -22660,10 +22738,10 @@
     </row>
     <row r="68" spans="1:47">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C68" s="2">
         <v>45822.5831712963</v>
@@ -22684,16 +22762,16 @@
         <v>2760</v>
       </c>
       <c r="I68" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="L68" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="M68">
         <v>104</v>
@@ -22729,7 +22807,7 @@
         <v>-3.495</v>
       </c>
       <c r="AE68" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF68">
         <v>0.022222</v>
@@ -22782,10 +22860,10 @@
     </row>
     <row r="69" spans="1:47">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C69" s="2">
         <v>45822.58351851852</v>
@@ -22806,16 +22884,16 @@
         <v>2790</v>
       </c>
       <c r="I69" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="L69" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="M69">
         <v>126</v>
@@ -22851,7 +22929,7 @@
         <v>-3.434</v>
       </c>
       <c r="AE69" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF69">
         <v>0.006667</v>
@@ -22904,10 +22982,10 @@
     </row>
     <row r="70" spans="1:47">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C70" s="2">
         <v>45822.58386574074</v>
@@ -22928,16 +23006,16 @@
         <v>2820</v>
       </c>
       <c r="I70" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="L70" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="M70">
         <v>102</v>
@@ -22973,7 +23051,7 @@
         <v>-3.59666667</v>
       </c>
       <c r="AE70" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF70">
         <v>-0.017778</v>
@@ -23026,10 +23104,10 @@
     </row>
     <row r="71" spans="1:47">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C71" s="2">
         <v>45822.58456018518</v>
@@ -23050,16 +23128,16 @@
         <v>2880</v>
       </c>
       <c r="I71" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="L71" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="M71">
         <v>120</v>
@@ -23095,7 +23173,7 @@
         <v>-3.67283333</v>
       </c>
       <c r="AE71" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF71">
         <v>-0.004167</v>
@@ -23148,10 +23226,10 @@
     </row>
     <row r="72" spans="1:47">
       <c r="A72" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C72" s="2">
         <v>45822.58525462963</v>
@@ -23172,16 +23250,16 @@
         <v>2940</v>
       </c>
       <c r="I72" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="L72" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="M72">
         <v>118</v>
@@ -23217,7 +23295,7 @@
         <v>-3.92683333</v>
       </c>
       <c r="AE72" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF72">
         <v>-0.013889</v>
@@ -23270,10 +23348,10 @@
     </row>
     <row r="73" spans="1:47">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C73" s="2">
         <v>45822.58560185185</v>
@@ -23294,16 +23372,16 @@
         <v>2970</v>
       </c>
       <c r="I73" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="L73" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="M73">
         <v>130</v>
@@ -23339,7 +23417,7 @@
         <v>-3.932</v>
       </c>
       <c r="AE73" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF73">
         <v>-0.000556</v>
@@ -23392,10 +23470,10 @@
     </row>
     <row r="74" spans="1:47">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C74" s="2">
         <v>45822.58594907408</v>
@@ -23416,16 +23494,16 @@
         <v>3000</v>
       </c>
       <c r="I74" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="L74" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="M74">
         <v>106</v>
@@ -23461,7 +23539,7 @@
         <v>-3.81</v>
       </c>
       <c r="AE74" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF74">
         <v>0.013333</v>
@@ -23514,10 +23592,10 @@
     </row>
     <row r="75" spans="1:47">
       <c r="A75" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C75" s="2">
         <v>45822.58629629629</v>
@@ -23538,16 +23616,16 @@
         <v>3030</v>
       </c>
       <c r="I75" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="L75" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="M75">
         <v>130</v>
@@ -23583,7 +23661,7 @@
         <v>-3.617</v>
       </c>
       <c r="AE75" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF75">
         <v>0.021111</v>
@@ -23636,10 +23714,10 @@
     </row>
     <row r="76" spans="1:47">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C76" s="2">
         <v>45822.58664351852</v>
@@ -23660,16 +23738,16 @@
         <v>3060</v>
       </c>
       <c r="I76" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="L76" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="M76">
         <v>97</v>
@@ -23705,7 +23783,7 @@
         <v>-3.617</v>
       </c>
       <c r="AE76" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF76">
         <v>0</v>
@@ -23758,10 +23836,10 @@
     </row>
     <row r="77" spans="1:47">
       <c r="A77" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C77" s="2">
         <v>45822.58699074074</v>
@@ -23782,16 +23860,16 @@
         <v>3090</v>
       </c>
       <c r="I77" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="L77" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="M77">
         <v>104</v>
@@ -23827,7 +23905,7 @@
         <v>-3.26133333</v>
       </c>
       <c r="AE77" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF77">
         <v>0.038889</v>
@@ -23880,10 +23958,10 @@
     </row>
     <row r="78" spans="1:47">
       <c r="A78" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C78" s="2">
         <v>45822.58733796296</v>
@@ -23904,16 +23982,16 @@
         <v>3120</v>
       </c>
       <c r="I78" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="L78" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="M78">
         <v>104</v>
@@ -23949,7 +24027,7 @@
         <v>-3.119</v>
       </c>
       <c r="AE78" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF78">
         <v>0.015556</v>
@@ -24002,10 +24080,10 @@
     </row>
     <row r="79" spans="1:47">
       <c r="A79" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C79" s="2">
         <v>45822.58768518519</v>
@@ -24026,16 +24104,16 @@
         <v>3150</v>
       </c>
       <c r="I79" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="L79" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="M79">
         <v>73</v>
@@ -24071,7 +24149,7 @@
         <v>-3.01766667</v>
       </c>
       <c r="AE79" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF79">
         <v>0.011111</v>
@@ -24124,10 +24202,10 @@
     </row>
     <row r="80" spans="1:47">
       <c r="A80" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C80" s="2">
         <v>45822.58803240741</v>
@@ -24148,16 +24226,16 @@
         <v>3180</v>
       </c>
       <c r="I80" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L80" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="M80">
         <v>87</v>
@@ -24193,7 +24271,7 @@
         <v>-3.424</v>
       </c>
       <c r="AE80" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF80">
         <v>-0.044444</v>
@@ -24246,10 +24324,10 @@
     </row>
     <row r="81" spans="1:47">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B81" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C81" s="2">
         <v>45822.58872685185</v>
@@ -24270,16 +24348,16 @@
         <v>3240</v>
       </c>
       <c r="I81" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="L81" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="M81">
         <v>69</v>
@@ -24315,7 +24393,7 @@
         <v>-3.66766667</v>
       </c>
       <c r="AE81" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF81">
         <v>-0.013333</v>
@@ -24368,10 +24446,10 @@
     </row>
     <row r="82" spans="1:47">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C82" s="2">
         <v>45822.58907407407</v>
@@ -24392,16 +24470,16 @@
         <v>3270</v>
       </c>
       <c r="I82" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="L82" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="M82">
         <v>106</v>
@@ -24437,7 +24515,7 @@
         <v>-3.69833333</v>
       </c>
       <c r="AE82" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF82">
         <v>-0.003333</v>
@@ -24490,10 +24568,10 @@
     </row>
     <row r="83" spans="1:47">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C83" s="2">
         <v>45822.5894212963</v>
@@ -24514,16 +24592,16 @@
         <v>3300</v>
       </c>
       <c r="I83" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="L83" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="M83">
         <v>108</v>
@@ -24559,7 +24637,7 @@
         <v>-3.69833333</v>
       </c>
       <c r="AE83" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF83">
         <v>0</v>
@@ -24612,10 +24690,10 @@
     </row>
     <row r="84" spans="1:47">
       <c r="A84" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C84" s="2">
         <v>45822.58976851852</v>
@@ -24636,16 +24714,16 @@
         <v>3330</v>
       </c>
       <c r="I84" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="L84" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="M84">
         <v>90</v>
@@ -24681,7 +24759,7 @@
         <v>-3.51533333</v>
       </c>
       <c r="AE84" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF84">
         <v>0.02</v>
@@ -24734,10 +24812,10 @@
     </row>
     <row r="85" spans="1:47">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C85" s="2">
         <v>45822.59011574074</v>
@@ -24758,16 +24836,16 @@
         <v>3360</v>
       </c>
       <c r="I85" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="L85" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="M85">
         <v>99</v>
@@ -24803,7 +24881,7 @@
         <v>-3.312</v>
       </c>
       <c r="AE85" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF85">
         <v>0.022222</v>
@@ -24856,10 +24934,10 @@
     </row>
     <row r="86" spans="1:47">
       <c r="A86" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C86" s="2">
         <v>45822.59046296297</v>
@@ -24880,16 +24958,16 @@
         <v>3390</v>
       </c>
       <c r="I86" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="L86" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="M86">
         <v>75</v>
@@ -24925,7 +25003,7 @@
         <v>-3.33266667</v>
       </c>
       <c r="AE86" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF86">
         <v>-0.002222</v>
@@ -24978,10 +25056,10 @@
     </row>
     <row r="87" spans="1:47">
       <c r="A87" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C87" s="2">
         <v>45822.59081018518</v>
@@ -25002,16 +25080,16 @@
         <v>3420</v>
       </c>
       <c r="I87" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="L87" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="M87">
         <v>96</v>
@@ -25047,7 +25125,7 @@
         <v>-3.40333333</v>
       </c>
       <c r="AE87" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF87">
         <v>-0.007778</v>
@@ -25100,10 +25178,10 @@
     </row>
     <row r="88" spans="1:47">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B88" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C88" s="2">
         <v>45822.59115740741</v>
@@ -25124,16 +25202,16 @@
         <v>3450</v>
       </c>
       <c r="I88" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="L88" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="M88">
         <v>57</v>
@@ -25169,7 +25247,7 @@
         <v>-3.33266667</v>
       </c>
       <c r="AE88" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF88">
         <v>0.007778</v>
@@ -25222,10 +25300,10 @@
     </row>
     <row r="89" spans="1:47">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C89" s="2">
         <v>45822.59150462963</v>
@@ -25246,16 +25324,16 @@
         <v>3480</v>
       </c>
       <c r="I89" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="L89" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="M89">
         <v>82</v>
@@ -25291,7 +25369,7 @@
         <v>-3.26133333</v>
       </c>
       <c r="AE89" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF89">
         <v>0.007778</v>
@@ -25344,10 +25422,10 @@
     </row>
     <row r="90" spans="1:47">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C90" s="2">
         <v>45822.59185185185</v>
@@ -25368,16 +25446,16 @@
         <v>3510</v>
       </c>
       <c r="I90" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="L90" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="M90">
         <v>47</v>
@@ -25413,7 +25491,7 @@
         <v>-3.14966667</v>
       </c>
       <c r="AE90" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF90">
         <v>0.012222</v>
@@ -25466,10 +25544,10 @@
     </row>
     <row r="91" spans="1:47">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C91" s="2">
         <v>45822.5925462963</v>
@@ -25490,16 +25568,16 @@
         <v>3570</v>
       </c>
       <c r="I91" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J91" t="b">
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="L91" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="M91">
         <v>82</v>
@@ -25535,7 +25613,7 @@
         <v>-3.22583333</v>
       </c>
       <c r="AE91" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF91">
         <v>-0.004167</v>
@@ -25588,10 +25666,10 @@
     </row>
     <row r="92" spans="1:47">
       <c r="A92" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C92" s="2">
         <v>45822.59289351852</v>
@@ -25612,16 +25690,16 @@
         <v>3600</v>
       </c>
       <c r="I92" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J92" t="b">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="L92" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="M92">
         <v>76</v>
@@ -25657,7 +25735,7 @@
         <v>-3.33233333</v>
       </c>
       <c r="AE92" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF92">
         <v>-0.011667</v>
@@ -25710,10 +25788,10 @@
     </row>
     <row r="93" spans="1:47">
       <c r="A93" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C93" s="2">
         <v>45822.59324074074</v>
@@ -25734,16 +25812,16 @@
         <v>3630</v>
       </c>
       <c r="I93" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J93" t="b">
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="L93" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="M93">
         <v>89</v>
@@ -25779,7 +25857,7 @@
         <v>-3.50533333</v>
       </c>
       <c r="AE93" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF93">
         <v>-0.018889</v>
@@ -25832,10 +25910,10 @@
     </row>
     <row r="94" spans="1:47">
       <c r="A94" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C94" s="2">
         <v>45822.59393518518</v>
@@ -25856,16 +25934,16 @@
         <v>3690</v>
       </c>
       <c r="I94" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J94" t="b">
         <v>1</v>
       </c>
       <c r="K94" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="L94" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="M94">
         <v>63</v>
@@ -25901,7 +25979,7 @@
         <v>-3.54583333</v>
       </c>
       <c r="AE94" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF94">
         <v>-0.002222</v>
@@ -25954,10 +26032,10 @@
     </row>
     <row r="95" spans="1:47">
       <c r="A95" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B95" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C95" s="2">
         <v>45822.59428240741</v>
@@ -25978,16 +26056,16 @@
         <v>3720</v>
       </c>
       <c r="I95" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J95" t="b">
         <v>1</v>
       </c>
       <c r="K95" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="L95" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="M95">
         <v>65</v>
@@ -26023,7 +26101,7 @@
         <v>-3.54566667</v>
       </c>
       <c r="AE95" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF95">
         <v>0</v>
@@ -26076,10 +26154,10 @@
     </row>
     <row r="96" spans="1:47">
       <c r="A96" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B96" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C96" s="2">
         <v>45822.59462962963</v>
@@ -26100,16 +26178,16 @@
         <v>3750</v>
       </c>
       <c r="I96" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J96" t="b">
         <v>1</v>
       </c>
       <c r="K96" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="L96" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="M96">
         <v>49</v>
@@ -26145,7 +26223,7 @@
         <v>-3.51533333</v>
       </c>
       <c r="AE96" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF96">
         <v>0.003333</v>
@@ -26198,10 +26276,10 @@
     </row>
     <row r="97" spans="1:47">
       <c r="A97" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C97" s="2">
         <v>45822.59497685185</v>
@@ -26222,16 +26300,16 @@
         <v>3780</v>
       </c>
       <c r="I97" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J97" t="b">
         <v>1</v>
       </c>
       <c r="K97" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="L97" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="M97">
         <v>77</v>
@@ -26267,7 +26345,7 @@
         <v>-3.099</v>
       </c>
       <c r="AE97" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF97">
         <v>0.045556</v>
@@ -26320,10 +26398,10 @@
     </row>
     <row r="98" spans="1:47">
       <c r="A98" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B98" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C98" s="2">
         <v>45822.59532407407</v>
@@ -26344,16 +26422,16 @@
         <v>3810</v>
       </c>
       <c r="I98" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J98" t="b">
         <v>1</v>
       </c>
       <c r="K98" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="L98" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="M98">
         <v>93</v>
@@ -26389,7 +26467,7 @@
         <v>-2.91566667</v>
       </c>
       <c r="AE98" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF98">
         <v>0.02</v>
@@ -26442,10 +26520,10 @@
     </row>
     <row r="99" spans="1:47">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B99" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C99" s="2">
         <v>45822.59567129629</v>
@@ -26466,16 +26544,16 @@
         <v>3840</v>
       </c>
       <c r="I99" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J99" t="b">
         <v>1</v>
       </c>
       <c r="K99" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="L99" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="M99">
         <v>89</v>
@@ -26511,7 +26589,7 @@
         <v>-3.048</v>
       </c>
       <c r="AE99" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF99">
         <v>-0.014444</v>
@@ -26564,10 +26642,10 @@
     </row>
     <row r="100" spans="1:47">
       <c r="A100" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B100" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C100" s="2">
         <v>45822.59601851852</v>
@@ -26588,16 +26666,16 @@
         <v>3870</v>
       </c>
       <c r="I100" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J100" t="b">
         <v>1</v>
       </c>
       <c r="K100" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="L100" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="M100">
         <v>96</v>
@@ -26633,7 +26711,7 @@
         <v>-3.11933333</v>
       </c>
       <c r="AE100" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF100">
         <v>-0.007778</v>
@@ -26686,10 +26764,10 @@
     </row>
     <row r="101" spans="1:47">
       <c r="A101" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B101" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C101" s="2">
         <v>45822.59636574074</v>
@@ -26710,16 +26788,16 @@
         <v>3900</v>
       </c>
       <c r="I101" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J101" t="b">
         <v>1</v>
       </c>
       <c r="K101" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="L101" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="M101">
         <v>103</v>
@@ -26755,7 +26833,7 @@
         <v>-2.72266667</v>
       </c>
       <c r="AE101" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF101">
         <v>0.043333</v>
@@ -26808,10 +26886,10 @@
     </row>
     <row r="102" spans="1:47">
       <c r="A102" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B102" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C102" s="2">
         <v>45822.59706018519</v>
@@ -26832,16 +26910,16 @@
         <v>3960</v>
       </c>
       <c r="I102" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J102" t="b">
         <v>1</v>
       </c>
       <c r="K102" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="L102" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="M102">
         <v>101</v>
@@ -26877,7 +26955,7 @@
         <v>-2.61633333</v>
       </c>
       <c r="AE102" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF102">
         <v>0.005833</v>
@@ -26930,10 +27008,10 @@
     </row>
     <row r="103" spans="1:47">
       <c r="A103" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B103" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C103" s="2">
         <v>45822.5974074074</v>
@@ -26954,16 +27032,16 @@
         <v>3990</v>
       </c>
       <c r="I103" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J103" t="b">
         <v>1</v>
       </c>
       <c r="K103" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="L103" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="M103">
         <v>78</v>
@@ -26999,7 +27077,7 @@
         <v>-2.225</v>
       </c>
       <c r="AE103" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF103">
         <v>0.042778</v>
@@ -27052,10 +27130,10 @@
     </row>
     <row r="104" spans="1:47">
       <c r="A104" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B104" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C104" s="2">
         <v>45822.59810185185</v>
@@ -27076,16 +27154,16 @@
         <v>4050</v>
       </c>
       <c r="I104" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J104" t="b">
         <v>1</v>
       </c>
       <c r="K104" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="L104" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="M104">
         <v>60</v>
@@ -27121,7 +27199,7 @@
         <v>-1.905</v>
       </c>
       <c r="AE104" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF104">
         <v>0.0175</v>
@@ -27174,10 +27252,10 @@
     </row>
     <row r="105" spans="1:47">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B105" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C105" s="2">
         <v>45822.59844907407</v>
@@ -27198,16 +27276,16 @@
         <v>4080</v>
       </c>
       <c r="I105" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J105" t="b">
         <v>1</v>
       </c>
       <c r="K105" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="L105" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="M105">
         <v>69</v>
@@ -27243,7 +27321,7 @@
         <v>-2.55</v>
       </c>
       <c r="AE105" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF105">
         <v>-0.07055599999999999</v>
@@ -27296,10 +27374,10 @@
     </row>
     <row r="106" spans="1:47">
       <c r="A106" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B106" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C106" s="2">
         <v>45822.5987962963</v>
@@ -27320,16 +27398,16 @@
         <v>4110</v>
       </c>
       <c r="I106" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J106" t="b">
         <v>1</v>
       </c>
       <c r="K106" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="L106" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="M106">
         <v>69</v>
@@ -27365,7 +27443,7 @@
         <v>-3.22066667</v>
       </c>
       <c r="AE106" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF106">
         <v>-0.073333</v>
@@ -27418,10 +27496,10 @@
     </row>
     <row r="107" spans="1:47">
       <c r="A107" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B107" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C107" s="2">
         <v>45822.59914351852</v>
@@ -27442,16 +27520,16 @@
         <v>4140</v>
       </c>
       <c r="I107" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J107" t="b">
         <v>1</v>
       </c>
       <c r="K107" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="L107" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="M107">
         <v>43</v>
@@ -27487,7 +27565,7 @@
         <v>-3.97266667</v>
       </c>
       <c r="AE107" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF107">
         <v>-0.082222</v>
@@ -27540,10 +27618,10 @@
     </row>
     <row r="108" spans="1:47">
       <c r="A108" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B108" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C108" s="2">
         <v>45822.59949074074</v>
@@ -27564,16 +27642,16 @@
         <v>4170</v>
       </c>
       <c r="I108" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J108" t="b">
         <v>1</v>
       </c>
       <c r="K108" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="L108" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="M108">
         <v>36</v>
@@ -27609,7 +27687,7 @@
         <v>-3.739</v>
       </c>
       <c r="AE108" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF108">
         <v>0.025556</v>
@@ -27662,10 +27740,10 @@
     </row>
     <row r="109" spans="1:47">
       <c r="A109" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B109" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C109" s="2">
         <v>45822.59983796296</v>
@@ -27686,16 +27764,16 @@
         <v>4200</v>
       </c>
       <c r="I109" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J109" t="b">
         <v>1</v>
       </c>
       <c r="K109" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="L109" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="M109">
         <v>50</v>
@@ -27731,7 +27809,7 @@
         <v>-3.749</v>
       </c>
       <c r="AE109" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF109">
         <v>-0.001111</v>
@@ -27784,10 +27862,10 @@
     </row>
     <row r="110" spans="1:47">
       <c r="A110" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B110" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C110" s="2">
         <v>45822.60018518518</v>
@@ -27808,16 +27886,16 @@
         <v>4230</v>
       </c>
       <c r="I110" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J110" t="b">
         <v>1</v>
       </c>
       <c r="K110" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="L110" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="M110">
         <v>4</v>
@@ -27853,7 +27931,7 @@
         <v>-3.251</v>
       </c>
       <c r="AE110" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF110">
         <v>0.054444</v>
@@ -27906,10 +27984,10 @@
     </row>
     <row r="111" spans="1:47">
       <c r="A111" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B111" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C111" s="2">
         <v>45822.60053240741</v>
@@ -27930,16 +28008,16 @@
         <v>4260</v>
       </c>
       <c r="I111" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J111" t="b">
         <v>1</v>
       </c>
       <c r="K111" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="L111" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="M111">
         <v>24</v>
@@ -27975,7 +28053,7 @@
         <v>-2.784</v>
       </c>
       <c r="AE111" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF111">
         <v>0.051111</v>
@@ -28028,10 +28106,10 @@
     </row>
     <row r="112" spans="1:47">
       <c r="A112" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B112" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C112" s="2">
         <v>45822.6012962963</v>
@@ -28052,16 +28130,16 @@
         <v>4320</v>
       </c>
       <c r="I112" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J112" t="b">
         <v>1</v>
       </c>
       <c r="K112" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="L112" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="M112">
         <v>35</v>
@@ -28097,7 +28175,7 @@
         <v>-3.34766667</v>
       </c>
       <c r="AE112" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF112">
         <v>-0.030833</v>
@@ -28150,10 +28228,10 @@
     </row>
     <row r="113" spans="1:47">
       <c r="A113" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B113" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C113" s="2">
         <v>45822.60157407408</v>
@@ -28174,16 +28252,16 @@
         <v>4350</v>
       </c>
       <c r="I113" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J113" t="b">
         <v>1</v>
       </c>
       <c r="K113" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="L113" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="M113">
         <v>85</v>
@@ -28219,7 +28297,7 @@
         <v>-3.33266667</v>
       </c>
       <c r="AE113" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF113">
         <v>0.001667</v>
@@ -28272,10 +28350,10 @@
     </row>
     <row r="114" spans="1:47">
       <c r="A114" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B114" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C114" s="2">
         <v>45822.60192129629</v>
@@ -28296,16 +28374,16 @@
         <v>4380</v>
       </c>
       <c r="I114" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J114" t="b">
         <v>1</v>
       </c>
       <c r="K114" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="L114" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="M114">
         <v>12</v>
@@ -28341,7 +28419,7 @@
         <v>-4.17566667</v>
       </c>
       <c r="AE114" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF114">
         <v>-0.092222</v>
@@ -28394,10 +28472,10 @@
     </row>
     <row r="115" spans="1:47">
       <c r="A115" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B115" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C115" s="2">
         <v>45822.60226851852</v>
@@ -28418,16 +28496,16 @@
         <v>4410</v>
       </c>
       <c r="I115" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J115" t="b">
         <v>1</v>
       </c>
       <c r="K115" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="L115" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="M115">
         <v>166</v>
@@ -28463,7 +28541,7 @@
         <v>-3.302</v>
       </c>
       <c r="AE115" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="AF115">
         <v>0.095556</v>
